--- a/marketing_surveys/012_pet_product_packaging_preference_survey--marketing_surveys.xlsx
+++ b/marketing_surveys/012_pet_product_packaging_preference_survey--marketing_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -692,8 +692,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -721,12 +721,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'cardboard'}</t>
+          <t>cardboard</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Cardboard'}</t>
+          <t>Cardboard</t>
         </is>
       </c>
     </row>
@@ -738,12 +738,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'paper'}</t>
+          <t>paper</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Paper'}</t>
+          <t>Paper</t>
         </is>
       </c>
     </row>
@@ -755,12 +755,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'plastic'}</t>
+          <t>plastic</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Plastic'}</t>
+          <t>Plastic</t>
         </is>
       </c>
     </row>
@@ -772,12 +772,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'reducing_waste'}</t>
+          <t>reducing_waste</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Reducing waste'}</t>
+          <t>Reducing waste</t>
         </is>
       </c>
     </row>
@@ -789,12 +789,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'environmental_concerns'}</t>
+          <t>environmental_concerns</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Environmental concerns'}</t>
+          <t>Environmental concerns</t>
         </is>
       </c>
     </row>
@@ -806,12 +806,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'cost'}</t>
+          <t>cost</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Cost'}</t>
+          <t>Cost</t>
         </is>
       </c>
     </row>
@@ -823,12 +823,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'convenience'}</t>
+          <t>convenience</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Convenience'}</t>
+          <t>Convenience</t>
         </is>
       </c>
     </row>
